--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-18).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-18).xlsx
@@ -938,43 +938,43 @@
     <t>215</t>
   </si>
   <si>
-    <t>31</t>
+    <t>23</t>
   </si>
   <si>
-    <t>R$ 9.343,18</t>
+    <t>R$ 9.232,23</t>
   </si>
   <si>
-    <t>99.7</t>
+    <t>98.4</t>
   </si>
   <si>
-    <t>66.4</t>
+    <t>66.3</t>
   </si>
   <si>
-    <t>7.31</t>
+    <t>7.36</t>
   </si>
   <si>
-    <t>22.7</t>
+    <t>22.9</t>
   </si>
   <si>
-    <t>8.6</t>
+    <t>8.7</t>
   </si>
   <si>
-    <t>6.1</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>28.2%</t>
+    <t>28.1%</t>
   </si>
   <si>
-    <t>17.2%</t>
+    <t>16.9%</t>
   </si>
   <si>
-    <t>0.9%</t>
+    <t>1.0%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>3.2%</t>
+    <t>3.1%</t>
   </si>
   <si>
     <t>0.8%</t>
@@ -983,40 +983,43 @@
     <t>0.1%</t>
   </si>
   <si>
-    <t>6.2%</t>
+    <t>6.0%</t>
   </si>
   <si>
-    <t>2.2%</t>
+    <t>2.1%</t>
   </si>
   <si>
-    <t>2457.0</t>
+    <t>6.1%</t>
   </si>
   <si>
-    <t>2089.0</t>
+    <t>2524.0</t>
   </si>
   <si>
-    <t>113.0</t>
+    <t>2142.0</t>
+  </si>
+  <si>
+    <t>127.0</t>
   </si>
   <si>
     <t>28.0</t>
   </si>
   <si>
-    <t>387.0</t>
+    <t>394.0</t>
   </si>
   <si>
-    <t>100.0</t>
+    <t>101.0</t>
   </si>
   <si>
-    <t>13.0</t>
+    <t>14.0</t>
   </si>
   <si>
-    <t>750.0</t>
+    <t>766.0</t>
   </si>
   <si>
-    <t>263.0</t>
+    <t>271.0</t>
   </si>
   <si>
-    <t>756.0</t>
+    <t>776.0</t>
   </si>
   <si>
     <t>0.6%</t>
@@ -2209,7 +2212,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,35 +2242,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>16314.32</v>
+      </c>
+      <c r="N6" s="6">
+        <v>165</v>
+      </c>
+      <c r="O6" s="6">
+        <v>134</v>
+      </c>
+      <c r="P6" s="7">
+        <v>13.502710843373492</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>24.17549776119403</v>
+      </c>
+      <c r="R6" s="8">
+        <v>2.5021141791044776</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.21641791044776118</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.082089552238805971</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.029850746268656716</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.037313432835820892</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0.014925373134328358</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -9078,7 +9139,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9108,14 +9169,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>633.14999999999998</v>
+      </c>
+      <c r="N51" s="6">
+        <v>7</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>10.352385714285715</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>62.899999999999999</v>
+      </c>
+      <c r="R51" s="8">
+        <v>43.383324999999999</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10147,33 +10220,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>95</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.031578947368421054</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0.021052631578947368</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -10995,7 +11114,7 @@
         <v>19633</v>
       </c>
       <c r="B64" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C64" s="4">
         <v>51</v>
@@ -11023,35 +11142,93 @@
         <v>58</v>
       </c>
       <c r="L64" s="4"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="6"/>
-      <c r="O64" s="6"/>
-      <c r="P64" s="7"/>
-      <c r="Q64" s="8"/>
-      <c r="R64" s="8"/>
-      <c r="S64" s="8"/>
-      <c r="T64" s="9"/>
-      <c r="U64" s="9"/>
-      <c r="V64" s="9"/>
-      <c r="W64" s="9"/>
-      <c r="X64" s="9"/>
-      <c r="Y64" s="9"/>
-      <c r="Z64" s="9"/>
-      <c r="AA64" s="9"/>
-      <c r="AB64" s="9"/>
-      <c r="AC64" s="9"/>
-      <c r="AD64" s="6"/>
-      <c r="AE64" s="6"/>
-      <c r="AF64" s="6"/>
-      <c r="AG64" s="6"/>
-      <c r="AH64" s="6"/>
-      <c r="AI64" s="6"/>
-      <c r="AJ64" s="6"/>
-      <c r="AK64" s="6"/>
-      <c r="AL64" s="6"/>
-      <c r="AM64" s="6"/>
-      <c r="AN64" s="9"/>
-      <c r="AO64" s="6"/>
+      <c r="M64" s="5">
+        <v>7896.8599999999997</v>
+      </c>
+      <c r="N64" s="6">
+        <v>87</v>
+      </c>
+      <c r="O64" s="6">
+        <v>41</v>
+      </c>
+      <c r="P64" s="7">
+        <v>4.2874034883720933</v>
+      </c>
+      <c r="Q64" s="8">
+        <v>23.664634146341463</v>
+      </c>
+      <c r="R64" s="8">
+        <v>11.709999999999999</v>
+      </c>
+      <c r="S64" s="8">
+        <v>7</v>
+      </c>
+      <c r="T64" s="9">
+        <v>0.24390243902439024</v>
+      </c>
+      <c r="U64" s="9">
+        <v>0.68292682926829273</v>
+      </c>
+      <c r="V64" s="9">
+        <v>0.26829268292682928</v>
+      </c>
+      <c r="W64" s="9">
+        <v>0</v>
+      </c>
+      <c r="X64" s="9">
+        <v>0.097560975609756101</v>
+      </c>
+      <c r="Y64" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="9">
+        <v>0.097560975609756101</v>
+      </c>
+      <c r="AB64" s="9">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="AC64" s="9">
+        <v>0.43902439024390244</v>
+      </c>
+      <c r="AD64" s="6">
+        <v>40</v>
+      </c>
+      <c r="AE64" s="6">
+        <v>28</v>
+      </c>
+      <c r="AF64" s="6">
+        <v>11</v>
+      </c>
+      <c r="AG64" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI64" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL64" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM64" s="6">
+        <v>18</v>
+      </c>
+      <c r="AN64" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP64" s="4">
         <v>58</v>
       </c>
@@ -16577,7 +16754,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16607,35 +16784,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>8426.1700000000001</v>
+      </c>
+      <c r="N102" s="6">
+        <v>89</v>
+      </c>
+      <c r="O102" s="6">
+        <v>64</v>
+      </c>
+      <c r="P102" s="7">
+        <v>15.327592222222224</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>32.261457812499998</v>
+      </c>
+      <c r="R102" s="8">
+        <v>8.84375</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -23888,7 +24123,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -23918,35 +24153,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>5877.96</v>
+      </c>
+      <c r="N151" s="6">
+        <v>64</v>
+      </c>
+      <c r="O151" s="6">
+        <v>60</v>
+      </c>
+      <c r="P151" s="7">
+        <v>7.7458328124999998</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>17.540278333333333</v>
+      </c>
+      <c r="R151" s="8">
+        <v>3.0866071428571429</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0.016666666666666666</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -24770,7 +25063,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -24800,35 +25093,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>4256.1000000000004</v>
+      </c>
+      <c r="N157" s="6">
+        <v>43</v>
+      </c>
+      <c r="O157" s="6">
+        <v>37</v>
+      </c>
+      <c r="P157" s="7">
+        <v>5.8565883720930234</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>15.634235135135134</v>
+      </c>
+      <c r="R157" s="8">
+        <v>2.9148648648648647</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.54054054054054057</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -24869,7 +25220,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -24899,35 +25250,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>4253.7299999999996</v>
+      </c>
+      <c r="N158" s="6">
+        <v>41</v>
+      </c>
+      <c r="O158" s="6">
+        <v>35</v>
+      </c>
+      <c r="P158" s="7">
+        <v>6.0101634146341461</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>17.379048571428573</v>
+      </c>
+      <c r="R158" s="8">
+        <v>4.2557142857142853</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -25904,7 +26313,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -25934,35 +26343,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>6007.9099999999999</v>
+      </c>
+      <c r="N165" s="6">
+        <v>63</v>
+      </c>
+      <c r="O165" s="6">
+        <v>40</v>
+      </c>
+      <c r="P165" s="7">
+        <v>5.6912573770491806</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>14.333332500000001</v>
+      </c>
+      <c r="R165" s="8">
+        <v>2.0358974358974362</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
@@ -33479,43 +33946,43 @@
         <v>325</v>
       </c>
       <c t="s" r="AC217" s="11">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="AD217" s="11">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="AE217" s="11">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="AF217" s="11">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="AG217" s="11">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="AH217" s="11">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="AI217" s="11">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="AJ217" s="11">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="AK217" s="11">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="AL217" s="11">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="AM217" s="11">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="AN217" s="11">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="AO217" s="11">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AP217" s="12"/>
       <c t="s" r="AQ217" s="12">
@@ -33532,10 +33999,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX217" s="11">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="AY217" s="11">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AZ217" s="12"/>
       <c r="BA217" s="12"/>
